--- a/ipar40tk-server/simulator/baselines/low-rpm_idle_filled_simulator.xlsx
+++ b/ipar40tk-server/simulator/baselines/low-rpm_idle_filled_simulator.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COMPACT-MAPS\COMPACT-MAPS\ipar40tk-server\simulator\baselines\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bprof2025\COMPACT-MAPS\COMPACT-MAPS\ipar40tk-server\simulator\baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA2E4C6-ED88-4D38-B67E-3B5851DBABD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -6701,7 +6702,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -7014,15 +7015,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F713"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="1"/>
+    <col min="4" max="4" width="7.6640625" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>321</v>
       </c>
@@ -7042,7 +7046,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -7062,7 +7066,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7082,7 +7086,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -7102,7 +7106,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -7122,7 +7126,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -7142,7 +7146,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -7162,7 +7166,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -7182,7 +7186,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -7202,7 +7206,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -7222,7 +7226,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -7242,7 +7246,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -7262,7 +7266,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -7282,7 +7286,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -7302,7 +7306,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -7322,7 +7326,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -7342,7 +7346,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -7362,7 +7366,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -7382,7 +7386,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -7402,7 +7406,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -7422,7 +7426,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7442,7 +7446,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -7462,7 +7466,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -7482,7 +7486,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -7502,7 +7506,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -7522,7 +7526,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -7542,7 +7546,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -7562,7 +7566,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -7582,7 +7586,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -7602,7 +7606,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -7622,7 +7626,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -7642,7 +7646,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>29</v>
       </c>
@@ -7662,7 +7666,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>30</v>
       </c>
@@ -7682,7 +7686,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -7702,7 +7706,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>32</v>
       </c>
@@ -7722,7 +7726,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -7742,7 +7746,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -7762,7 +7766,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>35</v>
       </c>
@@ -7782,7 +7786,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>36</v>
       </c>
@@ -7802,7 +7806,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>37</v>
       </c>
@@ -7822,7 +7826,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>38</v>
       </c>
@@ -7842,7 +7846,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -7862,7 +7866,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -7882,7 +7886,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>41</v>
       </c>
@@ -7902,7 +7906,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>42</v>
       </c>
@@ -7922,7 +7926,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>43</v>
       </c>
@@ -7942,7 +7946,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>44</v>
       </c>
@@ -7962,7 +7966,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>45</v>
       </c>
@@ -7982,7 +7986,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -8002,7 +8006,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>47</v>
       </c>
@@ -8022,7 +8026,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>48</v>
       </c>
@@ -8042,7 +8046,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>49</v>
       </c>
@@ -8062,7 +8066,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>50</v>
       </c>
@@ -8082,7 +8086,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>51</v>
       </c>
@@ -8102,7 +8106,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>52</v>
       </c>
@@ -8122,7 +8126,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>53</v>
       </c>
@@ -8142,7 +8146,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>54</v>
       </c>
@@ -8162,7 +8166,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>55</v>
       </c>
@@ -8182,7 +8186,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>56</v>
       </c>
@@ -8202,7 +8206,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>57</v>
       </c>
@@ -8222,7 +8226,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>58</v>
       </c>
@@ -8242,7 +8246,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>59</v>
       </c>
@@ -8262,7 +8266,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>60</v>
       </c>
@@ -8282,7 +8286,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>61</v>
       </c>
@@ -8302,7 +8306,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>62</v>
       </c>
@@ -8322,7 +8326,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -8342,7 +8346,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>64</v>
       </c>
@@ -8362,7 +8366,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>65</v>
       </c>
@@ -8382,7 +8386,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>66</v>
       </c>
@@ -8402,7 +8406,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>67</v>
       </c>
@@ -8422,7 +8426,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>68</v>
       </c>
@@ -8442,7 +8446,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>69</v>
       </c>
@@ -8462,7 +8466,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>70</v>
       </c>
@@ -8482,7 +8486,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>71</v>
       </c>
@@ -8502,7 +8506,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>72</v>
       </c>
@@ -8522,7 +8526,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>73</v>
       </c>
@@ -8542,7 +8546,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>74</v>
       </c>
@@ -8562,7 +8566,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>75</v>
       </c>
@@ -8582,7 +8586,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>76</v>
       </c>
@@ -8602,7 +8606,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>77</v>
       </c>
@@ -8622,7 +8626,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>78</v>
       </c>
@@ -8642,7 +8646,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>79</v>
       </c>
@@ -8662,7 +8666,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>80</v>
       </c>
@@ -8682,7 +8686,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>81</v>
       </c>
@@ -8702,7 +8706,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>82</v>
       </c>
@@ -8722,7 +8726,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>83</v>
       </c>
@@ -8742,7 +8746,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>84</v>
       </c>
@@ -8762,7 +8766,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>85</v>
       </c>
@@ -8782,7 +8786,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>86</v>
       </c>
@@ -8802,7 +8806,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>87</v>
       </c>
@@ -8822,7 +8826,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>88</v>
       </c>
@@ -8842,7 +8846,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>89</v>
       </c>
@@ -8862,7 +8866,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>90</v>
       </c>
@@ -8882,7 +8886,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>91</v>
       </c>
@@ -8902,7 +8906,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>92</v>
       </c>
@@ -8922,7 +8926,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>93</v>
       </c>
@@ -8942,7 +8946,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>94</v>
       </c>
@@ -8962,7 +8966,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>95</v>
       </c>
@@ -8982,7 +8986,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>96</v>
       </c>
@@ -9002,7 +9006,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>97</v>
       </c>
@@ -9022,7 +9026,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>98</v>
       </c>
@@ -9042,7 +9046,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>99</v>
       </c>
@@ -9062,7 +9066,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>100</v>
       </c>
@@ -9082,7 +9086,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>101</v>
       </c>
@@ -9102,7 +9106,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -9122,7 +9126,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>103</v>
       </c>
@@ -9142,7 +9146,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>104</v>
       </c>
@@ -9162,7 +9166,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>105</v>
       </c>
@@ -9182,7 +9186,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>106</v>
       </c>
@@ -9202,7 +9206,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>107</v>
       </c>
@@ -9222,7 +9226,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>108</v>
       </c>
@@ -9242,7 +9246,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>109</v>
       </c>
@@ -9262,7 +9266,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>110</v>
       </c>
@@ -9282,7 +9286,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>111</v>
       </c>
@@ -9302,7 +9306,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>112</v>
       </c>
@@ -9322,7 +9326,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>113</v>
       </c>
@@ -9342,7 +9346,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>114</v>
       </c>
@@ -9362,7 +9366,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>115</v>
       </c>
@@ -9382,7 +9386,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>116</v>
       </c>
@@ -9402,7 +9406,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>117</v>
       </c>
@@ -9422,7 +9426,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>118</v>
       </c>
@@ -9442,7 +9446,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>119</v>
       </c>
@@ -9462,7 +9466,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>120</v>
       </c>
@@ -9482,7 +9486,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>121</v>
       </c>
@@ -9502,7 +9506,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>122</v>
       </c>
@@ -9522,7 +9526,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>123</v>
       </c>
@@ -9542,7 +9546,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>124</v>
       </c>
@@ -9562,7 +9566,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>125</v>
       </c>
@@ -9582,7 +9586,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>126</v>
       </c>
@@ -9602,7 +9606,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>127</v>
       </c>
@@ -9622,7 +9626,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>128</v>
       </c>
@@ -9642,7 +9646,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>129</v>
       </c>
@@ -9662,7 +9666,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>130</v>
       </c>
@@ -9682,7 +9686,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>131</v>
       </c>
@@ -9702,7 +9706,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>132</v>
       </c>
@@ -9722,7 +9726,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>133</v>
       </c>
@@ -9742,7 +9746,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>134</v>
       </c>
@@ -9762,7 +9766,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>135</v>
       </c>
@@ -9782,7 +9786,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>136</v>
       </c>
@@ -9802,7 +9806,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>137</v>
       </c>
@@ -9822,7 +9826,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>138</v>
       </c>
@@ -9842,7 +9846,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>139</v>
       </c>
@@ -9862,7 +9866,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>140</v>
       </c>
@@ -9882,7 +9886,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>141</v>
       </c>
@@ -9902,7 +9906,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>142</v>
       </c>
@@ -9922,7 +9926,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>143</v>
       </c>
@@ -9942,7 +9946,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>144</v>
       </c>
@@ -9962,7 +9966,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>145</v>
       </c>
@@ -9982,7 +9986,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>146</v>
       </c>
@@ -10002,7 +10006,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>147</v>
       </c>
@@ -10022,7 +10026,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>135</v>
       </c>
@@ -10042,7 +10046,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>148</v>
       </c>
@@ -10062,7 +10066,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>149</v>
       </c>
@@ -10082,7 +10086,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>150</v>
       </c>
@@ -10102,7 +10106,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>151</v>
       </c>
@@ -10122,7 +10126,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>152</v>
       </c>
@@ -10142,7 +10146,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>153</v>
       </c>
@@ -10162,7 +10166,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>154</v>
       </c>
@@ -10182,7 +10186,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>155</v>
       </c>
@@ -10202,7 +10206,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>156</v>
       </c>
@@ -10222,7 +10226,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>157</v>
       </c>
@@ -10242,7 +10246,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>158</v>
       </c>
@@ -10262,7 +10266,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>159</v>
       </c>
@@ -10282,7 +10286,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>160</v>
       </c>
@@ -10302,7 +10306,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>161</v>
       </c>
@@ -10322,7 +10326,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>162</v>
       </c>
@@ -10342,7 +10346,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>163</v>
       </c>
@@ -10362,7 +10366,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>164</v>
       </c>
@@ -10382,7 +10386,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>165</v>
       </c>
@@ -10402,7 +10406,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>166</v>
       </c>
@@ -10422,7 +10426,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>167</v>
       </c>
@@ -10442,7 +10446,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>168</v>
       </c>
@@ -10462,7 +10466,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>169</v>
       </c>
@@ -10482,7 +10486,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>170</v>
       </c>
@@ -10502,7 +10506,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>171</v>
       </c>
@@ -10522,7 +10526,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>172</v>
       </c>
@@ -10542,7 +10546,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>173</v>
       </c>
@@ -10562,7 +10566,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>174</v>
       </c>
@@ -10582,7 +10586,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>175</v>
       </c>
@@ -10602,7 +10606,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>176</v>
       </c>
@@ -10622,7 +10626,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>177</v>
       </c>
@@ -10642,7 +10646,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>178</v>
       </c>
@@ -10662,7 +10666,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>179</v>
       </c>
@@ -10682,7 +10686,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>180</v>
       </c>
@@ -10702,7 +10706,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>181</v>
       </c>
@@ -10722,7 +10726,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>182</v>
       </c>
@@ -10742,7 +10746,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>183</v>
       </c>
@@ -10762,7 +10766,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>184</v>
       </c>
@@ -10782,7 +10786,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>185</v>
       </c>
@@ -10802,7 +10806,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>186</v>
       </c>
@@ -10822,7 +10826,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>187</v>
       </c>
@@ -10842,7 +10846,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>188</v>
       </c>
@@ -10862,7 +10866,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>189</v>
       </c>
@@ -10882,7 +10886,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>190</v>
       </c>
@@ -10902,7 +10906,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>191</v>
       </c>
@@ -10922,7 +10926,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>192</v>
       </c>
@@ -10942,7 +10946,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>193</v>
       </c>
@@ -10962,7 +10966,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>194</v>
       </c>
@@ -10982,7 +10986,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>195</v>
       </c>
@@ -11002,7 +11006,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>196</v>
       </c>
@@ -11022,7 +11026,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>197</v>
       </c>
@@ -11042,7 +11046,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>198</v>
       </c>
@@ -11062,7 +11066,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>199</v>
       </c>
@@ -11082,7 +11086,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>200</v>
       </c>
@@ -11102,7 +11106,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>201</v>
       </c>
@@ -11122,7 +11126,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>202</v>
       </c>
@@ -11142,7 +11146,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>203</v>
       </c>
@@ -11162,7 +11166,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>204</v>
       </c>
@@ -11182,7 +11186,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>205</v>
       </c>
@@ -11202,7 +11206,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>206</v>
       </c>
@@ -11222,7 +11226,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>207</v>
       </c>
@@ -11242,7 +11246,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>208</v>
       </c>
@@ -11262,7 +11266,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>209</v>
       </c>
@@ -11282,7 +11286,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>210</v>
       </c>
@@ -11302,7 +11306,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>211</v>
       </c>
@@ -11322,7 +11326,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>212</v>
       </c>
@@ -11342,7 +11346,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>213</v>
       </c>
@@ -11362,7 +11366,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>214</v>
       </c>
@@ -11382,7 +11386,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>215</v>
       </c>
@@ -11402,7 +11406,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>216</v>
       </c>
@@ -11422,7 +11426,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>217</v>
       </c>
@@ -11442,7 +11446,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>218</v>
       </c>
@@ -11462,7 +11466,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>219</v>
       </c>
@@ -11482,7 +11486,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>220</v>
       </c>
@@ -11502,7 +11506,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>221</v>
       </c>
@@ -11522,7 +11526,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>222</v>
       </c>
@@ -11542,7 +11546,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>223</v>
       </c>
@@ -11562,7 +11566,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>144</v>
       </c>
@@ -11582,7 +11586,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>224</v>
       </c>
@@ -11602,7 +11606,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>225</v>
       </c>
@@ -11622,7 +11626,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>226</v>
       </c>
@@ -11642,7 +11646,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>227</v>
       </c>
@@ -11662,7 +11666,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>228</v>
       </c>
@@ -11682,7 +11686,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>229</v>
       </c>
@@ -11702,7 +11706,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>230</v>
       </c>
@@ -11722,7 +11726,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>231</v>
       </c>
@@ -11742,7 +11746,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>232</v>
       </c>
@@ -11762,7 +11766,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>233</v>
       </c>
@@ -11782,7 +11786,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>234</v>
       </c>
@@ -11802,7 +11806,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>235</v>
       </c>
@@ -11822,7 +11826,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>236</v>
       </c>
@@ -11842,7 +11846,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>237</v>
       </c>
@@ -11862,7 +11866,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>238</v>
       </c>
@@ -11882,7 +11886,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>239</v>
       </c>
@@ -11902,7 +11906,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>240</v>
       </c>
@@ -11922,7 +11926,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>241</v>
       </c>
@@ -11942,7 +11946,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>242</v>
       </c>
@@ -11962,7 +11966,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>243</v>
       </c>
@@ -11982,7 +11986,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>244</v>
       </c>
@@ -12002,7 +12006,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>245</v>
       </c>
@@ -12022,7 +12026,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>246</v>
       </c>
@@ -12042,7 +12046,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>247</v>
       </c>
@@ -12062,7 +12066,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>248</v>
       </c>
@@ -12082,7 +12086,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>249</v>
       </c>
@@ -12102,7 +12106,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>250</v>
       </c>
@@ -12122,7 +12126,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>251</v>
       </c>
@@ -12142,7 +12146,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>252</v>
       </c>
@@ -12162,7 +12166,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>253</v>
       </c>
@@ -12182,7 +12186,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>254</v>
       </c>
@@ -12202,7 +12206,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>255</v>
       </c>
@@ -12222,7 +12226,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>256</v>
       </c>
@@ -12242,7 +12246,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>257</v>
       </c>
@@ -12262,7 +12266,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>258</v>
       </c>
@@ -12282,7 +12286,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>259</v>
       </c>
@@ -12302,7 +12306,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>260</v>
       </c>
@@ -12322,7 +12326,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>261</v>
       </c>
@@ -12342,7 +12346,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>262</v>
       </c>
@@ -12362,7 +12366,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>263</v>
       </c>
@@ -12382,7 +12386,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>264</v>
       </c>
@@ -12402,7 +12406,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>265</v>
       </c>
@@ -12422,7 +12426,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>266</v>
       </c>
@@ -12442,7 +12446,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>267</v>
       </c>
@@ -12462,7 +12466,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>268</v>
       </c>
@@ -12482,7 +12486,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>269</v>
       </c>
@@ -12502,7 +12506,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>270</v>
       </c>
@@ -12522,7 +12526,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>271</v>
       </c>
@@ -12542,7 +12546,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>272</v>
       </c>
@@ -12562,7 +12566,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>273</v>
       </c>
@@ -12582,7 +12586,7 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>274</v>
       </c>
@@ -12602,7 +12606,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>275</v>
       </c>
@@ -12622,7 +12626,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>276</v>
       </c>
@@ -12642,7 +12646,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>277</v>
       </c>
@@ -12662,7 +12666,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>278</v>
       </c>
@@ -12682,7 +12686,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>279</v>
       </c>
@@ -12702,7 +12706,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>280</v>
       </c>
@@ -12722,7 +12726,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>281</v>
       </c>
@@ -12742,7 +12746,7 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>282</v>
       </c>
@@ -12762,7 +12766,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>283</v>
       </c>
@@ -12782,7 +12786,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>284</v>
       </c>
@@ -12802,7 +12806,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>285</v>
       </c>
@@ -12822,7 +12826,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>286</v>
       </c>
@@ -12842,7 +12846,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>287</v>
       </c>
@@ -12862,7 +12866,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>288</v>
       </c>
@@ -12882,7 +12886,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>289</v>
       </c>
@@ -12902,7 +12906,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>290</v>
       </c>
@@ -12922,7 +12926,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>291</v>
       </c>
@@ -12942,7 +12946,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>292</v>
       </c>
@@ -12962,7 +12966,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>293</v>
       </c>
@@ -12982,7 +12986,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>294</v>
       </c>
@@ -13002,7 +13006,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>295</v>
       </c>
@@ -13022,7 +13026,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>296</v>
       </c>
@@ -13042,7 +13046,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>297</v>
       </c>
@@ -13062,7 +13066,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>298</v>
       </c>
@@ -13082,7 +13086,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>299</v>
       </c>
@@ -13102,7 +13106,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>300</v>
       </c>
@@ -13122,7 +13126,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>301</v>
       </c>
@@ -13142,7 +13146,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>302</v>
       </c>
@@ -13162,7 +13166,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>303</v>
       </c>
@@ -13182,7 +13186,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>304</v>
       </c>
@@ -13202,7 +13206,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>305</v>
       </c>
@@ -13222,7 +13226,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>306</v>
       </c>
@@ -13242,7 +13246,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>307</v>
       </c>
@@ -13262,7 +13266,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>308</v>
       </c>
@@ -13282,7 +13286,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>309</v>
       </c>
@@ -13302,7 +13306,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>310</v>
       </c>
@@ -13322,7 +13326,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>311</v>
       </c>
@@ -13342,7 +13346,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>312</v>
       </c>
@@ -13362,7 +13366,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>313</v>
       </c>
@@ -13382,7 +13386,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>314</v>
       </c>
@@ -13402,7 +13406,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>315</v>
       </c>
@@ -13422,7 +13426,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>316</v>
       </c>
@@ -13442,7 +13446,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>317</v>
       </c>
@@ -13462,7 +13466,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>318</v>
       </c>
@@ -13482,7 +13486,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>319</v>
       </c>
@@ -13502,7 +13506,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>320</v>
       </c>
@@ -13522,7 +13526,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B326" t="s">
         <v>402</v>
       </c>
@@ -13536,7 +13540,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D327" t="s">
         <v>854</v>
       </c>
@@ -13547,7 +13551,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D328" t="s">
         <v>855</v>
       </c>
@@ -13558,7 +13562,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D329" t="s">
         <v>856</v>
       </c>
@@ -13569,7 +13573,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D330" t="s">
         <v>857</v>
       </c>
@@ -13580,7 +13584,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D331" t="s">
         <v>850</v>
       </c>
@@ -13591,7 +13595,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D332" t="s">
         <v>851</v>
       </c>
@@ -13602,7 +13606,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D333" t="s">
         <v>852</v>
       </c>
@@ -13613,7 +13617,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D334" t="s">
         <v>853</v>
       </c>
@@ -13624,7 +13628,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D335" t="s">
         <v>854</v>
       </c>
@@ -13635,7 +13639,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D336" t="s">
         <v>855</v>
       </c>
@@ -13646,7 +13650,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="337" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D337" t="s">
         <v>856</v>
       </c>
@@ -13657,7 +13661,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="338" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D338" t="s">
         <v>858</v>
       </c>
@@ -13668,7 +13672,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="339" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D339" t="s">
         <v>859</v>
       </c>
@@ -13679,7 +13683,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="340" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D340" t="s">
         <v>860</v>
       </c>
@@ -13690,7 +13694,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="341" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D341" t="s">
         <v>861</v>
       </c>
@@ -13701,7 +13705,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="342" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D342" t="s">
         <v>862</v>
       </c>
@@ -13712,7 +13716,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="343" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D343" t="s">
         <v>863</v>
       </c>
@@ -13723,7 +13727,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="344" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D344" t="s">
         <v>864</v>
       </c>
@@ -13734,7 +13738,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="345" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D345" t="s">
         <v>865</v>
       </c>
@@ -13745,7 +13749,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="346" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D346" t="s">
         <v>866</v>
       </c>
@@ -13756,7 +13760,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="347" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D347" t="s">
         <v>867</v>
       </c>
@@ -13767,7 +13771,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="348" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D348" t="s">
         <v>868</v>
       </c>
@@ -13778,7 +13782,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="349" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D349" t="s">
         <v>869</v>
       </c>
@@ -13789,7 +13793,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="350" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D350" t="s">
         <v>870</v>
       </c>
@@ -13800,7 +13804,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="351" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D351" t="s">
         <v>871</v>
       </c>
@@ -13811,7 +13815,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="352" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D352" t="s">
         <v>872</v>
       </c>
@@ -13822,7 +13826,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="353" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D353" t="s">
         <v>873</v>
       </c>
@@ -13833,7 +13837,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="354" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D354" t="s">
         <v>874</v>
       </c>
@@ -13844,7 +13848,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="355" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D355" t="s">
         <v>875</v>
       </c>
@@ -13855,7 +13859,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="356" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D356" t="s">
         <v>876</v>
       </c>
@@ -13866,7 +13870,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="357" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D357" t="s">
         <v>877</v>
       </c>
@@ -13877,7 +13881,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="358" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D358" t="s">
         <v>878</v>
       </c>
@@ -13888,7 +13892,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="359" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D359" t="s">
         <v>879</v>
       </c>
@@ -13899,7 +13903,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="360" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D360" t="s">
         <v>880</v>
       </c>
@@ -13910,7 +13914,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="361" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D361" t="s">
         <v>881</v>
       </c>
@@ -13921,7 +13925,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="362" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D362" t="s">
         <v>882</v>
       </c>
@@ -13932,7 +13936,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="363" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D363" t="s">
         <v>883</v>
       </c>
@@ -13943,7 +13947,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="364" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D364" t="s">
         <v>884</v>
       </c>
@@ -13954,7 +13958,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="365" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D365" t="s">
         <v>885</v>
       </c>
@@ -13965,7 +13969,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="366" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D366" t="s">
         <v>886</v>
       </c>
@@ -13976,7 +13980,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="367" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D367" t="s">
         <v>887</v>
       </c>
@@ -13987,7 +13991,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="368" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D368" t="s">
         <v>888</v>
       </c>
@@ -13998,7 +14002,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="369" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D369" t="s">
         <v>889</v>
       </c>
@@ -14009,7 +14013,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="370" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D370" t="s">
         <v>890</v>
       </c>
@@ -14020,7 +14024,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="371" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D371" t="s">
         <v>891</v>
       </c>
@@ -14031,7 +14035,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="372" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D372" t="s">
         <v>892</v>
       </c>
@@ -14042,7 +14046,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="373" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D373" t="s">
         <v>893</v>
       </c>
@@ -14053,7 +14057,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="374" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D374" t="s">
         <v>894</v>
       </c>
@@ -14064,7 +14068,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="375" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D375" t="s">
         <v>895</v>
       </c>
@@ -14075,7 +14079,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="376" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D376" t="s">
         <v>896</v>
       </c>
@@ -14086,7 +14090,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="377" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D377" t="s">
         <v>897</v>
       </c>
@@ -14097,7 +14101,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="378" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D378" t="s">
         <v>898</v>
       </c>
@@ -14108,7 +14112,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="379" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D379" t="s">
         <v>891</v>
       </c>
@@ -14119,7 +14123,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="380" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D380" t="s">
         <v>892</v>
       </c>
@@ -14130,7 +14134,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="381" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D381" t="s">
         <v>893</v>
       </c>
@@ -14141,7 +14145,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="382" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D382" t="s">
         <v>894</v>
       </c>
@@ -14152,7 +14156,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="383" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D383" t="s">
         <v>895</v>
       </c>
@@ -14163,7 +14167,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="384" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D384" t="s">
         <v>896</v>
       </c>
@@ -14174,7 +14178,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="385" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D385" t="s">
         <v>897</v>
       </c>
@@ -14185,7 +14189,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="386" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D386" t="s">
         <v>899</v>
       </c>
@@ -14196,7 +14200,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="387" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D387" t="s">
         <v>900</v>
       </c>
@@ -14207,7 +14211,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="388" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D388" t="s">
         <v>901</v>
       </c>
@@ -14218,7 +14222,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="389" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D389" t="s">
         <v>902</v>
       </c>
@@ -14229,7 +14233,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="390" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D390" t="s">
         <v>903</v>
       </c>
@@ -14240,7 +14244,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="391" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D391" t="s">
         <v>904</v>
       </c>
@@ -14251,7 +14255,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="392" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D392" t="s">
         <v>905</v>
       </c>
@@ -14262,7 +14266,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="393" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D393" t="s">
         <v>906</v>
       </c>
@@ -14273,7 +14277,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="394" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D394" t="s">
         <v>907</v>
       </c>
@@ -14284,7 +14288,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="395" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D395" t="s">
         <v>908</v>
       </c>
@@ -14295,7 +14299,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="396" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D396" t="s">
         <v>909</v>
       </c>
@@ -14306,7 +14310,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="397" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D397" t="s">
         <v>910</v>
       </c>
@@ -14317,7 +14321,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="398" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D398" t="s">
         <v>911</v>
       </c>
@@ -14328,7 +14332,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="399" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D399" t="s">
         <v>912</v>
       </c>
@@ -14339,7 +14343,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="400" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D400" t="s">
         <v>913</v>
       </c>
@@ -14350,7 +14354,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="401" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D401" t="s">
         <v>914</v>
       </c>
@@ -14361,7 +14365,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="402" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D402" t="s">
         <v>915</v>
       </c>
@@ -14372,7 +14376,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="403" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D403" t="s">
         <v>908</v>
       </c>
@@ -14383,7 +14387,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="404" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D404" t="s">
         <v>909</v>
       </c>
@@ -14394,7 +14398,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="405" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D405" t="s">
         <v>910</v>
       </c>
@@ -14405,7 +14409,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="406" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D406" t="s">
         <v>911</v>
       </c>
@@ -14416,7 +14420,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="407" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D407" t="s">
         <v>912</v>
       </c>
@@ -14427,7 +14431,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="408" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D408" t="s">
         <v>913</v>
       </c>
@@ -14438,7 +14442,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="409" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D409" t="s">
         <v>914</v>
       </c>
@@ -14449,7 +14453,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="410" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D410" t="s">
         <v>916</v>
       </c>
@@ -14460,7 +14464,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="411" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D411" t="s">
         <v>917</v>
       </c>
@@ -14471,7 +14475,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="412" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D412" t="s">
         <v>918</v>
       </c>
@@ -14482,7 +14486,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="413" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D413" t="s">
         <v>919</v>
       </c>
@@ -14493,7 +14497,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="414" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D414" t="s">
         <v>920</v>
       </c>
@@ -14504,7 +14508,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="415" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D415" t="s">
         <v>921</v>
       </c>
@@ -14515,7 +14519,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="416" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D416" t="s">
         <v>922</v>
       </c>
@@ -14526,7 +14530,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="417" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D417" t="s">
         <v>923</v>
       </c>
@@ -14537,7 +14541,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="418" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D418" t="s">
         <v>924</v>
       </c>
@@ -14548,7 +14552,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="419" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D419" t="s">
         <v>917</v>
       </c>
@@ -14559,7 +14563,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="420" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D420" t="s">
         <v>918</v>
       </c>
@@ -14570,7 +14574,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="421" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D421" t="s">
         <v>919</v>
       </c>
@@ -14581,7 +14585,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="422" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D422" t="s">
         <v>920</v>
       </c>
@@ -14592,7 +14596,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="423" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D423" t="s">
         <v>921</v>
       </c>
@@ -14603,7 +14607,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="424" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D424" t="s">
         <v>922</v>
       </c>
@@ -14614,7 +14618,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="425" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D425" t="s">
         <v>923</v>
       </c>
@@ -14625,7 +14629,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="426" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D426" t="s">
         <v>925</v>
       </c>
@@ -14636,7 +14640,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="427" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D427" t="s">
         <v>926</v>
       </c>
@@ -14647,7 +14651,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="428" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D428" t="s">
         <v>927</v>
       </c>
@@ -14658,7 +14662,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="429" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D429" t="s">
         <v>928</v>
       </c>
@@ -14669,7 +14673,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="430" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D430" t="s">
         <v>929</v>
       </c>
@@ -14680,7 +14684,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="431" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D431" t="s">
         <v>930</v>
       </c>
@@ -14691,7 +14695,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="432" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D432" t="s">
         <v>931</v>
       </c>
@@ -14702,7 +14706,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="433" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D433" t="s">
         <v>932</v>
       </c>
@@ -14713,7 +14717,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="434" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D434" t="s">
         <v>933</v>
       </c>
@@ -14724,7 +14728,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="435" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D435" t="s">
         <v>926</v>
       </c>
@@ -14735,7 +14739,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="436" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D436" t="s">
         <v>927</v>
       </c>
@@ -14746,7 +14750,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="437" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D437" t="s">
         <v>928</v>
       </c>
@@ -14757,7 +14761,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="438" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D438" t="s">
         <v>929</v>
       </c>
@@ -14768,7 +14772,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="439" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D439" t="s">
         <v>930</v>
       </c>
@@ -14779,7 +14783,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="440" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D440" t="s">
         <v>931</v>
       </c>
@@ -14790,7 +14794,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="441" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D441" t="s">
         <v>932</v>
       </c>
@@ -14801,7 +14805,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="442" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D442" t="s">
         <v>934</v>
       </c>
@@ -14812,7 +14816,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="443" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D443" t="s">
         <v>935</v>
       </c>
@@ -14823,7 +14827,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="444" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D444" t="s">
         <v>936</v>
       </c>
@@ -14834,7 +14838,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="445" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D445" t="s">
         <v>937</v>
       </c>
@@ -14845,7 +14849,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="446" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D446" t="s">
         <v>938</v>
       </c>
@@ -14856,7 +14860,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="447" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D447" t="s">
         <v>939</v>
       </c>
@@ -14867,7 +14871,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="448" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D448" t="s">
         <v>940</v>
       </c>
@@ -14878,7 +14882,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="449" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D449" t="s">
         <v>941</v>
       </c>
@@ -14889,7 +14893,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="450" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D450" t="s">
         <v>942</v>
       </c>
@@ -14900,7 +14904,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="451" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D451" t="s">
         <v>943</v>
       </c>
@@ -14911,7 +14915,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="452" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D452" t="s">
         <v>944</v>
       </c>
@@ -14922,7 +14926,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="453" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D453" t="s">
         <v>945</v>
       </c>
@@ -14933,7 +14937,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="454" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D454" t="s">
         <v>946</v>
       </c>
@@ -14944,7 +14948,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="455" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D455" t="s">
         <v>947</v>
       </c>
@@ -14955,7 +14959,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="456" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D456" t="s">
         <v>948</v>
       </c>
@@ -14966,7 +14970,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="457" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D457" t="s">
         <v>949</v>
       </c>
@@ -14977,7 +14981,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="458" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D458" t="s">
         <v>950</v>
       </c>
@@ -14988,7 +14992,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="459" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D459" t="s">
         <v>951</v>
       </c>
@@ -14999,7 +15003,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="460" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D460" t="s">
         <v>952</v>
       </c>
@@ -15010,7 +15014,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="461" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D461" t="s">
         <v>953</v>
       </c>
@@ -15021,7 +15025,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="462" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D462" t="s">
         <v>954</v>
       </c>
@@ -15032,7 +15036,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="463" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D463" t="s">
         <v>955</v>
       </c>
@@ -15043,7 +15047,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="464" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D464" t="s">
         <v>956</v>
       </c>
@@ -15054,7 +15058,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="465" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D465" t="s">
         <v>957</v>
       </c>
@@ -15065,7 +15069,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="466" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D466" t="s">
         <v>958</v>
       </c>
@@ -15076,7 +15080,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="467" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D467" t="s">
         <v>959</v>
       </c>
@@ -15087,7 +15091,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="468" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D468" t="s">
         <v>960</v>
       </c>
@@ -15098,7 +15102,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="469" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D469" t="s">
         <v>961</v>
       </c>
@@ -15109,7 +15113,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="470" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D470" t="s">
         <v>962</v>
       </c>
@@ -15120,7 +15124,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="471" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D471" t="s">
         <v>963</v>
       </c>
@@ -15131,7 +15135,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="472" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D472" t="s">
         <v>964</v>
       </c>
@@ -15142,7 +15146,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="473" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D473" t="s">
         <v>965</v>
       </c>
@@ -15153,7 +15157,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="474" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D474" t="s">
         <v>966</v>
       </c>
@@ -15164,7 +15168,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="475" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D475" t="s">
         <v>967</v>
       </c>
@@ -15175,7 +15179,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="476" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D476" t="s">
         <v>968</v>
       </c>
@@ -15186,7 +15190,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="477" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D477" t="s">
         <v>969</v>
       </c>
@@ -15197,7 +15201,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="478" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D478" t="s">
         <v>970</v>
       </c>
@@ -15208,7 +15212,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="479" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D479" t="s">
         <v>971</v>
       </c>
@@ -15219,7 +15223,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="480" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D480" t="s">
         <v>972</v>
       </c>
@@ -15230,7 +15234,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="481" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D481" t="s">
         <v>973</v>
       </c>
@@ -15241,7 +15245,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="482" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D482" t="s">
         <v>974</v>
       </c>
@@ -15252,7 +15256,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="483" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D483" t="s">
         <v>975</v>
       </c>
@@ -15263,7 +15267,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="484" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D484" t="s">
         <v>976</v>
       </c>
@@ -15274,7 +15278,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="485" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D485" t="s">
         <v>977</v>
       </c>
@@ -15285,7 +15289,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="486" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D486" t="s">
         <v>978</v>
       </c>
@@ -15296,7 +15300,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="487" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D487" t="s">
         <v>979</v>
       </c>
@@ -15307,7 +15311,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="488" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D488" t="s">
         <v>980</v>
       </c>
@@ -15318,7 +15322,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="489" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D489" t="s">
         <v>981</v>
       </c>
@@ -15329,7 +15333,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="490" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D490" t="s">
         <v>982</v>
       </c>
@@ -15340,7 +15344,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="491" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D491" t="s">
         <v>983</v>
       </c>
@@ -15351,7 +15355,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="492" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D492" t="s">
         <v>984</v>
       </c>
@@ -15362,7 +15366,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="493" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D493" t="s">
         <v>985</v>
       </c>
@@ -15373,7 +15377,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="494" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D494" t="s">
         <v>986</v>
       </c>
@@ -15384,7 +15388,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="495" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D495" t="s">
         <v>987</v>
       </c>
@@ -15395,7 +15399,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="496" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D496" t="s">
         <v>988</v>
       </c>
@@ -15406,7 +15410,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="497" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D497" t="s">
         <v>989</v>
       </c>
@@ -15417,7 +15421,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="498" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D498" t="s">
         <v>990</v>
       </c>
@@ -15428,7 +15432,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="499" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D499" t="s">
         <v>991</v>
       </c>
@@ -15439,7 +15443,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="500" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D500" t="s">
         <v>992</v>
       </c>
@@ -15450,7 +15454,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="501" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D501" t="s">
         <v>993</v>
       </c>
@@ -15461,7 +15465,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="502" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D502" t="s">
         <v>994</v>
       </c>
@@ -15472,7 +15476,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="503" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D503" t="s">
         <v>995</v>
       </c>
@@ -15483,7 +15487,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="504" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D504" t="s">
         <v>996</v>
       </c>
@@ -15494,7 +15498,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="505" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D505" t="s">
         <v>997</v>
       </c>
@@ -15505,7 +15509,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="506" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D506" t="s">
         <v>998</v>
       </c>
@@ -15516,7 +15520,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="507" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D507" t="s">
         <v>999</v>
       </c>
@@ -15527,7 +15531,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="508" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D508" t="s">
         <v>1000</v>
       </c>
@@ -15538,7 +15542,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="509" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D509" t="s">
         <v>1001</v>
       </c>
@@ -15549,7 +15553,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="510" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D510" t="s">
         <v>1002</v>
       </c>
@@ -15560,7 +15564,7 @@
         <v>2076</v>
       </c>
     </row>
-    <row r="511" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D511" t="s">
         <v>1003</v>
       </c>
@@ -15571,7 +15575,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="512" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D512" t="s">
         <v>1004</v>
       </c>
@@ -15582,7 +15586,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="513" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D513" t="s">
         <v>1005</v>
       </c>
@@ -15593,7 +15597,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="514" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D514" t="s">
         <v>1006</v>
       </c>
@@ -15604,7 +15608,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="515" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D515" t="s">
         <v>1007</v>
       </c>
@@ -15615,7 +15619,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="516" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D516" t="s">
         <v>1008</v>
       </c>
@@ -15626,7 +15630,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="517" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D517" t="s">
         <v>1009</v>
       </c>
@@ -15637,7 +15641,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="518" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D518" t="s">
         <v>1010</v>
       </c>
@@ -15648,7 +15652,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="519" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D519" t="s">
         <v>1011</v>
       </c>
@@ -15659,7 +15663,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="520" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D520" t="s">
         <v>1012</v>
       </c>
@@ -15670,7 +15674,7 @@
         <v>2086</v>
       </c>
     </row>
-    <row r="521" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D521" t="s">
         <v>1013</v>
       </c>
@@ -15681,7 +15685,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="522" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D522" t="s">
         <v>1014</v>
       </c>
@@ -15692,7 +15696,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="523" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D523" t="s">
         <v>1015</v>
       </c>
@@ -15703,7 +15707,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="524" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D524" t="s">
         <v>1016</v>
       </c>
@@ -15714,7 +15718,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="525" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D525" t="s">
         <v>1017</v>
       </c>
@@ -15725,7 +15729,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="526" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D526" t="s">
         <v>1018</v>
       </c>
@@ -15736,7 +15740,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="527" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D527" t="s">
         <v>1019</v>
       </c>
@@ -15747,7 +15751,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="528" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D528" t="s">
         <v>1020</v>
       </c>
@@ -15758,7 +15762,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="529" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D529" t="s">
         <v>1021</v>
       </c>
@@ -15769,7 +15773,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="530" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D530" t="s">
         <v>1022</v>
       </c>
@@ -15780,7 +15784,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="531" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D531" t="s">
         <v>1015</v>
       </c>
@@ -15791,7 +15795,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="532" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D532" t="s">
         <v>1016</v>
       </c>
@@ -15802,7 +15806,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="533" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D533" t="s">
         <v>1017</v>
       </c>
@@ -15813,7 +15817,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="534" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D534" t="s">
         <v>1018</v>
       </c>
@@ -15824,7 +15828,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="535" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D535" t="s">
         <v>1019</v>
       </c>
@@ -15835,7 +15839,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="536" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D536" t="s">
         <v>1020</v>
       </c>
@@ -15846,7 +15850,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="537" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D537" t="s">
         <v>1021</v>
       </c>
@@ -15857,7 +15861,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="538" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D538" t="s">
         <v>1023</v>
       </c>
@@ -15868,7 +15872,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="539" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D539" t="s">
         <v>1024</v>
       </c>
@@ -15879,7 +15883,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="540" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D540" t="s">
         <v>1025</v>
       </c>
@@ -15890,7 +15894,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="541" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D541" t="s">
         <v>1026</v>
       </c>
@@ -15901,7 +15905,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="542" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D542" t="s">
         <v>1027</v>
       </c>
@@ -15912,7 +15916,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="543" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D543" t="s">
         <v>1028</v>
       </c>
@@ -15923,7 +15927,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="544" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D544" t="s">
         <v>1029</v>
       </c>
@@ -15934,7 +15938,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="545" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D545" t="s">
         <v>1030</v>
       </c>
@@ -15945,7 +15949,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="546" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D546" t="s">
         <v>1031</v>
       </c>
@@ -15956,7 +15960,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="547" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D547" t="s">
         <v>1024</v>
       </c>
@@ -15967,7 +15971,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="548" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D548" t="s">
         <v>1025</v>
       </c>
@@ -15978,7 +15982,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="549" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D549" t="s">
         <v>1026</v>
       </c>
@@ -15989,7 +15993,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="550" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D550" t="s">
         <v>1027</v>
       </c>
@@ -16000,7 +16004,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="551" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D551" t="s">
         <v>1028</v>
       </c>
@@ -16011,7 +16015,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="552" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D552" t="s">
         <v>1029</v>
       </c>
@@ -16022,7 +16026,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="553" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D553" t="s">
         <v>1030</v>
       </c>
@@ -16033,7 +16037,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="554" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D554" t="s">
         <v>1032</v>
       </c>
@@ -16044,7 +16048,7 @@
         <v>2106</v>
       </c>
     </row>
-    <row r="555" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D555" t="s">
         <v>1033</v>
       </c>
@@ -16055,7 +16059,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="556" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D556" t="s">
         <v>1034</v>
       </c>
@@ -16066,7 +16070,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="557" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D557" t="s">
         <v>1035</v>
       </c>
@@ -16077,7 +16081,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="558" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D558" t="s">
         <v>1036</v>
       </c>
@@ -16088,7 +16092,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="559" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D559" t="s">
         <v>1037</v>
       </c>
@@ -16099,7 +16103,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="560" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D560" t="s">
         <v>1038</v>
       </c>
@@ -16110,7 +16114,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="561" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D561" t="s">
         <v>1039</v>
       </c>
@@ -16121,7 +16125,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="562" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D562" t="s">
         <v>1040</v>
       </c>
@@ -16132,7 +16136,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="563" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D563" t="s">
         <v>1041</v>
       </c>
@@ -16143,7 +16147,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="564" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D564" t="s">
         <v>1042</v>
       </c>
@@ -16154,7 +16158,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="565" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D565" t="s">
         <v>1043</v>
       </c>
@@ -16165,7 +16169,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="566" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D566" t="s">
         <v>1044</v>
       </c>
@@ -16176,7 +16180,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="567" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D567" t="s">
         <v>1045</v>
       </c>
@@ -16187,7 +16191,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="568" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D568" t="s">
         <v>1046</v>
       </c>
@@ -16198,7 +16202,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="569" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D569" t="s">
         <v>1047</v>
       </c>
@@ -16209,7 +16213,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="570" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D570" t="s">
         <v>1048</v>
       </c>
@@ -16220,7 +16224,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="571" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D571" t="s">
         <v>1041</v>
       </c>
@@ -16231,7 +16235,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="572" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D572" t="s">
         <v>1042</v>
       </c>
@@ -16242,7 +16246,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="573" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D573" t="s">
         <v>1043</v>
       </c>
@@ -16253,7 +16257,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="574" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D574" t="s">
         <v>1044</v>
       </c>
@@ -16264,7 +16268,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="575" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D575" t="s">
         <v>1045</v>
       </c>
@@ -16275,7 +16279,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="576" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D576" t="s">
         <v>1046</v>
       </c>
@@ -16286,7 +16290,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="577" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D577" t="s">
         <v>1047</v>
       </c>
@@ -16297,7 +16301,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="578" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D578" t="s">
         <v>1049</v>
       </c>
@@ -16308,7 +16312,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="579" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D579" t="s">
         <v>1050</v>
       </c>
@@ -16319,7 +16323,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="580" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D580" t="s">
         <v>1051</v>
       </c>
@@ -16330,7 +16334,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="581" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D581" t="s">
         <v>1052</v>
       </c>
@@ -16341,7 +16345,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="582" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D582" t="s">
         <v>1053</v>
       </c>
@@ -16352,7 +16356,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="583" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D583" t="s">
         <v>1054</v>
       </c>
@@ -16363,7 +16367,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="584" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D584" t="s">
         <v>1055</v>
       </c>
@@ -16374,7 +16378,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="585" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D585" t="s">
         <v>1056</v>
       </c>
@@ -16385,7 +16389,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="586" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D586" t="s">
         <v>1057</v>
       </c>
@@ -16396,7 +16400,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="587" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D587" t="s">
         <v>1050</v>
       </c>
@@ -16407,7 +16411,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="588" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D588" t="s">
         <v>1051</v>
       </c>
@@ -16418,7 +16422,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="589" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D589" t="s">
         <v>1052</v>
       </c>
@@ -16429,7 +16433,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="590" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D590" t="s">
         <v>1053</v>
       </c>
@@ -16440,7 +16444,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="591" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D591" t="s">
         <v>1054</v>
       </c>
@@ -16451,7 +16455,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="592" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D592" t="s">
         <v>1055</v>
       </c>
@@ -16462,7 +16466,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="593" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D593" t="s">
         <v>1056</v>
       </c>
@@ -16473,7 +16477,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="594" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D594" t="s">
         <v>1058</v>
       </c>
@@ -16484,7 +16488,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="595" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D595" t="s">
         <v>1059</v>
       </c>
@@ -16495,7 +16499,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="596" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D596" t="s">
         <v>1060</v>
       </c>
@@ -16506,7 +16510,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="597" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D597" t="s">
         <v>1061</v>
       </c>
@@ -16517,7 +16521,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="598" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D598" t="s">
         <v>1062</v>
       </c>
@@ -16528,7 +16532,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="599" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D599" t="s">
         <v>1063</v>
       </c>
@@ -16539,7 +16543,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="600" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D600" t="s">
         <v>1064</v>
       </c>
@@ -16550,7 +16554,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="601" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D601" t="s">
         <v>1065</v>
       </c>
@@ -16561,7 +16565,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="602" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D602" t="s">
         <v>1066</v>
       </c>
@@ -16572,7 +16576,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="603" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D603" t="s">
         <v>1067</v>
       </c>
@@ -16583,7 +16587,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="604" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D604" t="s">
         <v>1068</v>
       </c>
@@ -16594,7 +16598,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="605" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D605" t="s">
         <v>1069</v>
       </c>
@@ -16605,7 +16609,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="606" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D606" t="s">
         <v>1070</v>
       </c>
@@ -16616,7 +16620,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="607" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D607" t="s">
         <v>1071</v>
       </c>
@@ -16627,7 +16631,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="608" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D608" t="s">
         <v>1072</v>
       </c>
@@ -16638,7 +16642,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="609" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D609" t="s">
         <v>1073</v>
       </c>
@@ -16649,7 +16653,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="610" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D610" t="s">
         <v>1074</v>
       </c>
@@ -16660,7 +16664,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="611" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D611" t="s">
         <v>1067</v>
       </c>
@@ -16671,7 +16675,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="612" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D612" t="s">
         <v>1068</v>
       </c>
@@ -16682,7 +16686,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="613" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D613" t="s">
         <v>1069</v>
       </c>
@@ -16693,7 +16697,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="614" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D614" t="s">
         <v>1070</v>
       </c>
@@ -16704,7 +16708,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="615" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D615" t="s">
         <v>1071</v>
       </c>
@@ -16715,7 +16719,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="616" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D616" t="s">
         <v>1072</v>
       </c>
@@ -16726,7 +16730,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="617" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D617" t="s">
         <v>1073</v>
       </c>
@@ -16737,7 +16741,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="618" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D618" t="s">
         <v>1075</v>
       </c>
@@ -16748,7 +16752,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="619" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D619" t="s">
         <v>1076</v>
       </c>
@@ -16759,7 +16763,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="620" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D620" t="s">
         <v>1077</v>
       </c>
@@ -16770,7 +16774,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="621" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D621" t="s">
         <v>1078</v>
       </c>
@@ -16781,7 +16785,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="622" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D622" t="s">
         <v>1079</v>
       </c>
@@ -16792,7 +16796,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="623" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D623" t="s">
         <v>1080</v>
       </c>
@@ -16803,7 +16807,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="624" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D624" t="s">
         <v>1081</v>
       </c>
@@ -16814,7 +16818,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="625" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D625" t="s">
         <v>1082</v>
       </c>
@@ -16825,7 +16829,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="626" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D626" t="s">
         <v>1083</v>
       </c>
@@ -16836,7 +16840,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="627" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D627" t="s">
         <v>1084</v>
       </c>
@@ -16847,7 +16851,7 @@
         <v>2158</v>
       </c>
     </row>
-    <row r="628" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D628" t="s">
         <v>1085</v>
       </c>
@@ -16858,7 +16862,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="629" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D629" t="s">
         <v>1086</v>
       </c>
@@ -16869,7 +16873,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="630" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D630" t="s">
         <v>1087</v>
       </c>
@@ -16880,7 +16884,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="631" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D631" t="s">
         <v>1088</v>
       </c>
@@ -16891,7 +16895,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="632" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D632" t="s">
         <v>1089</v>
       </c>
@@ -16902,7 +16906,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="633" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D633" t="s">
         <v>1090</v>
       </c>
@@ -16913,7 +16917,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="634" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D634" t="s">
         <v>1091</v>
       </c>
@@ -16924,7 +16928,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="635" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D635" t="s">
         <v>1092</v>
       </c>
@@ -16935,7 +16939,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="636" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D636" t="s">
         <v>1093</v>
       </c>
@@ -16946,7 +16950,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="637" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D637" t="s">
         <v>1094</v>
       </c>
@@ -16957,7 +16961,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="638" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D638" t="s">
         <v>1095</v>
       </c>
@@ -16968,7 +16972,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="639" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D639" t="s">
         <v>1096</v>
       </c>
@@ -16979,7 +16983,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="640" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D640" t="s">
         <v>1097</v>
       </c>
@@ -16990,7 +16994,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="641" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D641" t="s">
         <v>1098</v>
       </c>
@@ -17001,7 +17005,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="642" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D642" t="s">
         <v>1099</v>
       </c>
@@ -17012,7 +17016,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="643" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D643" t="s">
         <v>1092</v>
       </c>
@@ -17023,7 +17027,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="644" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D644" t="s">
         <v>1093</v>
       </c>
@@ -17034,7 +17038,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="645" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D645" t="s">
         <v>1094</v>
       </c>
@@ -17045,7 +17049,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="646" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D646" t="s">
         <v>1095</v>
       </c>
@@ -17056,7 +17060,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="647" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D647" t="s">
         <v>1096</v>
       </c>
@@ -17067,7 +17071,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="648" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D648" t="s">
         <v>1097</v>
       </c>
@@ -17078,7 +17082,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="649" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D649" t="s">
         <v>1098</v>
       </c>
@@ -17089,7 +17093,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="650" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D650" t="s">
         <v>1100</v>
       </c>
@@ -17100,7 +17104,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="651" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D651" t="s">
         <v>1101</v>
       </c>
@@ -17111,7 +17115,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="652" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D652" t="s">
         <v>1102</v>
       </c>
@@ -17122,7 +17126,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="653" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D653" t="s">
         <v>1103</v>
       </c>
@@ -17133,7 +17137,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="654" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D654" t="s">
         <v>1104</v>
       </c>
@@ -17144,7 +17148,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="655" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D655" t="s">
         <v>1105</v>
       </c>
@@ -17155,7 +17159,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="656" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D656" t="s">
         <v>1106</v>
       </c>
@@ -17166,7 +17170,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="657" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D657" t="s">
         <v>1107</v>
       </c>
@@ -17177,7 +17181,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="658" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D658" t="s">
         <v>1108</v>
       </c>
@@ -17188,7 +17192,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="659" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D659" t="s">
         <v>1109</v>
       </c>
@@ -17199,7 +17203,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="660" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D660" t="s">
         <v>1110</v>
       </c>
@@ -17210,7 +17214,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="661" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D661" t="s">
         <v>1111</v>
       </c>
@@ -17221,7 +17225,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="662" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D662" t="s">
         <v>1112</v>
       </c>
@@ -17232,7 +17236,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="663" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D663" t="s">
         <v>1113</v>
       </c>
@@ -17243,7 +17247,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="664" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D664" t="s">
         <v>1114</v>
       </c>
@@ -17254,7 +17258,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="665" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D665" t="s">
         <v>1115</v>
       </c>
@@ -17265,7 +17269,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="666" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D666" t="s">
         <v>1116</v>
       </c>
@@ -17276,7 +17280,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="667" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D667" t="s">
         <v>1117</v>
       </c>
@@ -17287,7 +17291,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="668" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D668" t="s">
         <v>1118</v>
       </c>
@@ -17298,7 +17302,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="669" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D669" t="s">
         <v>1119</v>
       </c>
@@ -17309,7 +17313,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="670" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D670" t="s">
         <v>1120</v>
       </c>
@@ -17320,7 +17324,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="671" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D671" t="s">
         <v>1121</v>
       </c>
@@ -17331,7 +17335,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="672" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D672" t="s">
         <v>1122</v>
       </c>
@@ -17342,7 +17346,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="673" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D673" t="s">
         <v>1123</v>
       </c>
@@ -17353,7 +17357,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="674" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D674" t="s">
         <v>1124</v>
       </c>
@@ -17364,7 +17368,7 @@
         <v>2198</v>
       </c>
     </row>
-    <row r="675" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D675" t="s">
         <v>1117</v>
       </c>
@@ -17375,7 +17379,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="676" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D676" t="s">
         <v>1118</v>
       </c>
@@ -17386,7 +17390,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="677" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D677" t="s">
         <v>1119</v>
       </c>
@@ -17397,7 +17401,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="678" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D678" t="s">
         <v>1120</v>
       </c>
@@ -17408,7 +17412,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="679" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D679" t="s">
         <v>1121</v>
       </c>
@@ -17419,7 +17423,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="680" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D680" t="s">
         <v>1122</v>
       </c>
@@ -17430,7 +17434,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="681" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D681" t="s">
         <v>1123</v>
       </c>
@@ -17441,7 +17445,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="682" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="682" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D682" t="s">
         <v>1125</v>
       </c>
@@ -17452,7 +17456,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="683" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D683" t="s">
         <v>1126</v>
       </c>
@@ -17463,7 +17467,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="684" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D684" t="s">
         <v>1127</v>
       </c>
@@ -17474,7 +17478,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="685" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="685" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D685" t="s">
         <v>1128</v>
       </c>
@@ -17485,7 +17489,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="686" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D686" t="s">
         <v>1129</v>
       </c>
@@ -17496,7 +17500,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="687" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D687" t="s">
         <v>1130</v>
       </c>
@@ -17507,7 +17511,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="688" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="688" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D688" t="s">
         <v>1131</v>
       </c>
@@ -17518,7 +17522,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="689" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="689" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D689" t="s">
         <v>1132</v>
       </c>
@@ -17529,7 +17533,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="690" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D690" t="s">
         <v>1133</v>
       </c>
@@ -17540,7 +17544,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="691" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D691" t="s">
         <v>1126</v>
       </c>
@@ -17551,7 +17555,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="692" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D692" t="s">
         <v>1127</v>
       </c>
@@ -17562,7 +17566,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="693" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D693" t="s">
         <v>1128</v>
       </c>
@@ -17573,7 +17577,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="694" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D694" t="s">
         <v>1129</v>
       </c>
@@ -17584,7 +17588,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="695" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D695" t="s">
         <v>1130</v>
       </c>
@@ -17595,7 +17599,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="696" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="696" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D696" t="s">
         <v>1131</v>
       </c>
@@ -17606,7 +17610,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="697" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D697" t="s">
         <v>1132</v>
       </c>
@@ -17617,7 +17621,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="698" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D698" t="s">
         <v>1134</v>
       </c>
@@ -17628,7 +17632,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="699" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D699" t="s">
         <v>1135</v>
       </c>
@@ -17639,7 +17643,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="700" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D700" t="s">
         <v>1136</v>
       </c>
@@ -17650,7 +17654,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="701" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D701" t="s">
         <v>1137</v>
       </c>
@@ -17661,7 +17665,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="702" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D702" t="s">
         <v>1138</v>
       </c>
@@ -17672,7 +17676,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="703" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D703" t="s">
         <v>1139</v>
       </c>
@@ -17683,7 +17687,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="704" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D704" t="s">
         <v>1140</v>
       </c>
@@ -17694,7 +17698,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="705" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D705" t="s">
         <v>1141</v>
       </c>
@@ -17705,7 +17709,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="706" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="706" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D706" t="s">
         <v>1142</v>
       </c>
@@ -17716,7 +17720,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="707" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D707" t="s">
         <v>1143</v>
       </c>
@@ -17727,7 +17731,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="708" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D708" t="s">
         <v>1144</v>
       </c>
@@ -17738,7 +17742,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="709" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="709" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D709" t="s">
         <v>1145</v>
       </c>
@@ -17749,7 +17753,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="710" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D710" t="s">
         <v>1146</v>
       </c>
@@ -17760,7 +17764,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="711" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D711" t="s">
         <v>1147</v>
       </c>
@@ -17771,7 +17775,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="712" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="712" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D712" t="s">
         <v>1148</v>
       </c>
@@ -17782,7 +17786,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="713" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D713" t="s">
         <v>1149</v>
       </c>
